--- a/src/ExcelsiorAspose.Tests/StyleTests.HeadingStyle.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/StyleTests.HeadingStyle.verified.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="2" r:id="DeterministicId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$5</definedName>

--- a/src/ExcelsiorAspose.Tests/StyleTests.HeadingStyle.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/StyleTests.HeadingStyle.verified.xlsx
@@ -529,7 +529,7 @@
     <col min="7" max="7" width="10.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="14" customHeight="1">
+    <row r="1" spans="1:7" ht="16" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -552,7 +552,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="14" customHeight="1">
+    <row r="2" spans="1:7" ht="16" customHeight="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -575,7 +575,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="14" customHeight="1">
+    <row r="3" spans="1:7" ht="16" customHeight="1">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -598,7 +598,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="14" customHeight="1">
+    <row r="4" spans="1:7" ht="16" customHeight="1">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -621,7 +621,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="14" customHeight="1">
+    <row r="5" spans="1:7" ht="16" customHeight="1">
       <c r="A5" s="2">
         <v>4</v>
       </c>

--- a/src/ExcelsiorAspose.Tests/StyleTests.HeadingStyle.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/StyleTests.HeadingStyle.verified.xlsx
@@ -529,7 +529,7 @@
     <col min="7" max="7" width="10.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16" customHeight="1">
+    <row r="1" spans="1:7" ht="14" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -552,7 +552,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="16" customHeight="1">
+    <row r="2" spans="1:7" ht="14" customHeight="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -575,7 +575,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16" customHeight="1">
+    <row r="3" spans="1:7" ht="14" customHeight="1">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -598,7 +598,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16" customHeight="1">
+    <row r="4" spans="1:7" ht="14" customHeight="1">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -621,7 +621,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16" customHeight="1">
+    <row r="5" spans="1:7" ht="14" customHeight="1">
       <c r="A5" s="2">
         <v>4</v>
       </c>
